--- a/data/gold/results/01_eriksen_replication/steenmeijer_table.xlsx
+++ b/data/gold/results/01_eriksen_replication/steenmeijer_table.xlsx
@@ -64,85 +64,85 @@
     <t>Bottom-up</t>
   </si>
   <si>
-    <t>4,864 (100·0%)</t>
-  </si>
-  <si>
-    <t>1,972 (40·6%)</t>
-  </si>
-  <si>
-    <t>1,340 (27·5%)</t>
-  </si>
-  <si>
-    <t>921 (18·9%)</t>
+    <t>4,608 (100·0%)</t>
+  </si>
+  <si>
+    <t>2,427 (52·7%)</t>
+  </si>
+  <si>
+    <t>1,395 (30·3%)</t>
+  </si>
+  <si>
+    <t>155 (3·4%)</t>
   </si>
   <si>
     <t>13 (0·3%)</t>
   </si>
   <si>
-    <t>12 (0·2%)</t>
-  </si>
-  <si>
-    <t>606 (12·5%)</t>
-  </si>
-  <si>
-    <t>5,595 (100·0%)</t>
-  </si>
-  <si>
-    <t>1,862 (33·3%)</t>
-  </si>
-  <si>
-    <t>2,924 (52·3%)</t>
-  </si>
-  <si>
-    <t>782 (14·0%)</t>
+    <t>12 (0·3%)</t>
+  </si>
+  <si>
+    <t>606 (13·2%)</t>
+  </si>
+  <si>
+    <t>4,261 (100·0%)</t>
+  </si>
+  <si>
+    <t>2,274 (53·4%)</t>
+  </si>
+  <si>
+    <t>1,829 (42·9%)</t>
+  </si>
+  <si>
+    <t>131 (3·1%)</t>
   </si>
   <si>
     <t>0 (&lt;0·1%)</t>
   </si>
   <si>
-    <t>28 (0·5%)</t>
-  </si>
-  <si>
-    <t>43 (100·0%)</t>
-  </si>
-  <si>
-    <t>16 (37·7%)</t>
-  </si>
-  <si>
-    <t>20 (46·6%)</t>
-  </si>
-  <si>
-    <t>7 (15·2%)</t>
-  </si>
-  <si>
-    <t>0 (0·4%)</t>
-  </si>
-  <si>
-    <t>3,833 (100·0%)</t>
-  </si>
-  <si>
-    <t>1,654 (43·1%)</t>
-  </si>
-  <si>
-    <t>1,647 (43·0%)</t>
-  </si>
-  <si>
-    <t>531 (13·9%)</t>
+    <t>28 (0·6%)</t>
+  </si>
+  <si>
+    <t>96 (100·0%)</t>
+  </si>
+  <si>
+    <t>44 (45·8%)</t>
+  </si>
+  <si>
+    <t>50 (51·8%)</t>
+  </si>
+  <si>
+    <t>2 (2·1%)</t>
+  </si>
+  <si>
+    <t>0 (0·2%)</t>
+  </si>
+  <si>
+    <t>4,856 (100·0%)</t>
+  </si>
+  <si>
+    <t>2,991 (61·6%)</t>
+  </si>
+  <si>
+    <t>1,759 (36·2%)</t>
+  </si>
+  <si>
+    <t>104 (2·1%)</t>
   </si>
   <si>
     <t>2 (&lt;0·1%)</t>
   </si>
   <si>
-    <t>1,479 (100·0%)</t>
-  </si>
-  <si>
-    <t>548 (37·1%)</t>
-  </si>
-  <si>
-    <t>701 (47·4%)</t>
-  </si>
-  <si>
-    <t>230 (15·6%)</t>
+    <t>833 (100·0%)</t>
+  </si>
+  <si>
+    <t>491 (59·0%)</t>
+  </si>
+  <si>
+    <t>305 (36·6%)</t>
+  </si>
+  <si>
+    <t>37 (4·4%)</t>
   </si>
   <si>
     <t>40,597 (100·0%)</t>

--- a/data/gold/results/01_eriksen_replication/steenmeijer_table.xlsx
+++ b/data/gold/results/01_eriksen_replication/steenmeijer_table.xlsx
@@ -64,13 +64,13 @@
     <t>Bottom-up</t>
   </si>
   <si>
-    <t>4,608 (100·0%)</t>
-  </si>
-  <si>
-    <t>2,427 (52·7%)</t>
-  </si>
-  <si>
-    <t>1,395 (30·3%)</t>
+    <t>4,629 (100·0%)</t>
+  </si>
+  <si>
+    <t>2,427 (52·4%)</t>
+  </si>
+  <si>
+    <t>1,395 (30·1%)</t>
   </si>
   <si>
     <t>155 (3·4%)</t>
@@ -82,7 +82,7 @@
     <t>12 (0·3%)</t>
   </si>
   <si>
-    <t>606 (13·2%)</t>
+    <t>627 (13·6%)</t>
   </si>
   <si>
     <t>4,261 (100·0%)</t>
@@ -133,16 +133,16 @@
     <t>2 (&lt;0·1%)</t>
   </si>
   <si>
-    <t>833 (100·0%)</t>
-  </si>
-  <si>
-    <t>491 (59·0%)</t>
-  </si>
-  <si>
-    <t>305 (36·6%)</t>
-  </si>
-  <si>
-    <t>37 (4·4%)</t>
+    <t>259 (100·0%)</t>
+  </si>
+  <si>
+    <t>163 (62·8%)</t>
+  </si>
+  <si>
+    <t>90 (34·8%)</t>
+  </si>
+  <si>
+    <t>6 (2·4%)</t>
   </si>
   <si>
     <t>40,597 (100·0%)</t>

--- a/data/gold/results/01_eriksen_replication/steenmeijer_table.xlsx
+++ b/data/gold/results/01_eriksen_replication/steenmeijer_table.xlsx
@@ -64,25 +64,25 @@
     <t>Bottom-up</t>
   </si>
   <si>
-    <t>4,629 (100·0%)</t>
-  </si>
-  <si>
-    <t>2,427 (52·4%)</t>
-  </si>
-  <si>
-    <t>1,395 (30·1%)</t>
-  </si>
-  <si>
-    <t>155 (3·4%)</t>
+    <t>4,715 (100·0%)</t>
+  </si>
+  <si>
+    <t>2,464 (52·3%)</t>
+  </si>
+  <si>
+    <t>1,442 (30·6%)</t>
+  </si>
+  <si>
+    <t>157 (3·3%)</t>
   </si>
   <si>
     <t>13 (0·3%)</t>
   </si>
   <si>
-    <t>12 (0·3%)</t>
-  </si>
-  <si>
-    <t>627 (13·6%)</t>
+    <t>12 (0·2%)</t>
+  </si>
+  <si>
+    <t>627 (13·3%)</t>
   </si>
   <si>
     <t>4,261 (100·0%)</t>

--- a/data/gold/results/01_eriksen_replication/steenmeijer_table.xlsx
+++ b/data/gold/results/01_eriksen_replication/steenmeijer_table.xlsx
@@ -64,13 +64,13 @@
     <t>Bottom-up</t>
   </si>
   <si>
-    <t>4,715 (100·0%)</t>
-  </si>
-  <si>
-    <t>2,464 (52·3%)</t>
-  </si>
-  <si>
-    <t>1,442 (30·6%)</t>
+    <t>4,713 (100·0%)</t>
+  </si>
+  <si>
+    <t>2,463 (52·3%)</t>
+  </si>
+  <si>
+    <t>1,441 (30·6%)</t>
   </si>
   <si>
     <t>157 (3·3%)</t>

--- a/data/gold/results/01_eriksen_replication/steenmeijer_table.xlsx
+++ b/data/gold/results/01_eriksen_replication/steenmeijer_table.xlsx
@@ -85,7 +85,7 @@
     <t>627 (13·3%)</t>
   </si>
   <si>
-    <t>4,261 (100·0%)</t>
+    <t>4,259 (100·0%)</t>
   </si>
   <si>
     <t>2,274 (53·4%)</t>
@@ -100,7 +100,7 @@
     <t>0 (&lt;0·1%)</t>
   </si>
   <si>
-    <t>28 (0·6%)</t>
+    <t>26 (0·6%)</t>
   </si>
   <si>
     <t>96 (100·0%)</t>
@@ -118,7 +118,7 @@
     <t>0 (0·2%)</t>
   </si>
   <si>
-    <t>4,856 (100·0%)</t>
+    <t>4,855 (100·0%)</t>
   </si>
   <si>
     <t>2,991 (61·6%)</t>
